--- a/projects/wanos-board/components.xlsx
+++ b/projects/wanos-board/components.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:K54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,7 +499,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>C725602</t>
+          <t>C6990958</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1246,7 +1246,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J15</t>
+          <t>J16</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -1254,22 +1254,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>KF301-3P</t>
+          <t>JST XH 4-pin</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>TerminalBlock_Phoenix_MKDS-2-5.08_1x03_P5.08mm</t>
+          <t>Connector_JST:JST_XH_B4B-XH-A_1x04_P2.50mm_Vertical</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>KF301-3P</t>
+          <t>B4B-XH-A</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>C39546</t>
+          <t>C158016</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1279,12 +1279,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>12V aux</t>
+          <t>LCD I2C both paralleled</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>12V</t>
+          <t>3.3V</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1301,7 +1301,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J16</t>
+          <t>U1</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -1309,32 +1309,32 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>JST XH 4-pin</t>
+          <t>PCA9554PW</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Connector_JST:JST_XH_B4B-XH-A_1x04_P2.50mm_Vertical</t>
+          <t>Package_SO:TSSOP-16_4.4x5mm_P0.65mm</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>B4B-XH-A</t>
+          <t>PCA9554PW</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>C158016</t>
+          <t>C112612</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>IC</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>LCD I2C both paralleled</t>
+          <t>I/O Expander A</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1344,19 +1344,19 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>TSSOP-16</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>SMT</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>U1</t>
+          <t>U2</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>I/O Expander A</t>
+          <t>I/O Expander B</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1411,7 +1411,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>U2</t>
+          <t>U4</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -1419,42 +1419,42 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>PCA9554PW</t>
+          <t>PC817 SMD</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Package_SO:TSSOP-16_4.4x5mm_P0.65mm</t>
+          <t>Optocoupler_SO-4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>PCA9554PW</t>
+          <t>PC817X</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>C112612</t>
+          <t>C106900</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>Optocoupler</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>I/O Expander B</t>
+          <t>12V presence</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3.3V</t>
+          <t>12V</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>TSSOP-16</t>
+          <t>SO-4</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1466,7 +1466,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>U4</t>
+          <t>U5</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -1474,42 +1474,42 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>PC817 SMD</t>
+          <t>TCA9546A</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Optocoupler_SO-4</t>
+          <t>Package_SO:TSSOP-16_4.4x5mm_P0.65mm</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>PC817X</t>
+          <t>TCA9546APWR</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>C106900</t>
+          <t>C133008</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Optocoupler</t>
+          <t>IC</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>12V presence</t>
+          <t>I2C mux 4ch SHT31</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>12V</t>
+          <t>3.3V</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>SO-4</t>
+          <t>TSSOP-16</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1521,7 +1521,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>U5</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -1529,42 +1529,42 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>TCA9546A</t>
+          <t>PN2222A</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Package_SO:TSSOP-16_4.4x5mm_P0.65mm</t>
+          <t>Package_TO_SOT_SMD:SOT-23</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>TCA9546APWR</t>
+          <t>PN2222A-TA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>C133008</t>
+          <t>C2150</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>Transistor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>I2C mux 4ch SHT31</t>
+          <t>SSR driver</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3.3V</t>
+          <t>12V</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>TSSOP-16</t>
+          <t>SOT-23</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1576,7 +1576,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -1631,7 +1631,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1686,7 +1686,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1741,7 +1741,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Q4</t>
+          <t>D1</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1749,32 +1749,32 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>PN2222A</t>
+          <t>SMBJ12A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Package_TO_SOT_SMD:SOT-23</t>
+          <t>Diode_SMD:D_SMB</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>PN2222A-TA</t>
+          <t>SMBJ12A</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>C2150</t>
+          <t>C149934</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Transistor</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>SSR driver</t>
+          <t>12V TVS</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>SOT-23</t>
+          <t>SMB</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1796,7 +1796,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>FB1</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1804,42 +1804,42 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SMBJ12A</t>
+          <t>BLM21PG331SN1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Diode_SMD:D_SMB</t>
+          <t>Inductor_SMD:L_0805</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>SMBJ12A</t>
+          <t>BLM21PG331SN1</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>C149934</t>
+          <t>C85832</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>Ferrite</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>12V TVS</t>
+          <t>Pi 5V filter</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>12V</t>
+          <t>5V</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>SMB</t>
+          <t>0805</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -1851,7 +1851,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FB1</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1859,42 +1859,37 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BLM21PG331SN1</t>
+          <t>470R</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Inductor_SMD:L_0805</t>
+          <t>Resistor_SMD:R_0603</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>BLM21PG331SN1</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>C85832</t>
+          <t>0603WAF4700T5E</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ferrite</t>
+          <t>Resistor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Pi 5V filter</t>
+          <t>SSR base</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>5V</t>
+          <t>3.3V</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0805</t>
+          <t>0603</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1906,7 +1901,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1927,7 +1922,6 @@
           <t>0603WAF4700T5E</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
           <t>Resistor</t>
@@ -1957,7 +1951,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R3</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -1978,7 +1972,6 @@
           <t>0603WAF4700T5E</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
           <t>Resistor</t>
@@ -2008,7 +2001,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>R3</t>
+          <t>R4</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -2029,7 +2022,6 @@
           <t>0603WAF4700T5E</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
           <t>Resistor</t>
@@ -2059,15 +2051,15 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>R4</t>
+          <t>R5-R8</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>470R</t>
+          <t>10k</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2077,10 +2069,9 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0603WAF4700T5E</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
+          <t>0603WAF1002T5E</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr">
         <is>
           <t>Resistor</t>
@@ -2088,7 +2079,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>SSR base</t>
+          <t>SSR pulldown</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2110,15 +2101,15 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>R5-R8</t>
+          <t>R9</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>10k</t>
+          <t>2k2</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2128,10 +2119,9 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0603WAF1002T5E</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
+          <t>0603WAF2201T5E</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
           <t>Resistor</t>
@@ -2139,7 +2129,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>SSR pulldown</t>
+          <t>I2C SCL pull-up</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2161,7 +2151,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>R9</t>
+          <t>R10</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -2182,7 +2172,6 @@
           <t>0603WAF2201T5E</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>Resistor</t>
@@ -2190,7 +2179,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>I2C SCL pull-up</t>
+          <t>I2C SDA pull-up</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2212,15 +2201,15 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>R10</t>
+          <t>R17-R28</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2k2</t>
+          <t>1k0</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2230,10 +2219,9 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0603WAF2201T5E</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
+          <t>0603WAF3300T5E</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
           <t>Resistor</t>
@@ -2241,7 +2229,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>I2C SDA pull-up</t>
+          <t>Activity LED</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2263,15 +2251,15 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>R17-R28</t>
+          <t>R29-R31</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>220R-330R</t>
+          <t>R29/R31=2k0 R30=6k8</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2281,10 +2269,9 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0603WAF3300T5E</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
+          <t>0603WAF2201T5E</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>Resistor</t>
@@ -2292,7 +2279,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Activity LED</t>
+          <t>Status LED</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2314,15 +2301,15 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>R29-R31</t>
+          <t>R32</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2k2-4k7</t>
+          <t>1k5</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2332,10 +2319,9 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0603WAF2201T5E</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
+          <t>0603WAF2001T5E</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>Resistor</t>
@@ -2343,12 +2329,12 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Status LED</t>
+          <t>Opto LED</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>3.3V</t>
+          <t>12V</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2365,7 +2351,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>R32</t>
+          <t>R33</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2373,7 +2359,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1k-2k2</t>
+          <t>10k</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2383,10 +2369,9 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0603WAF2001T5E</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
+          <t>0603WAF1002T5E</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>Resistor</t>
@@ -2394,7 +2379,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Opto LED</t>
+          <t>Opto RC filter</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2416,41 +2401,45 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>R33</t>
+          <t>C1-C12</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>10k</t>
+          <t>100nF</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Resistor_SMD:R_0603</t>
+          <t>Capacitor_SMD:C_0603</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0603WAF1002T5E</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
+          <t>CL10B104KB8NNNC</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>C14663</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Resistor</t>
+          <t>Capacitor</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Opto RC filter</t>
+          <t>Decoupling debounce</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>12V</t>
+          <t>3.3V</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2467,15 +2456,15 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>C1-C12</t>
+          <t>C13-C16</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>100nF</t>
+          <t>1uF</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2485,12 +2474,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>CL10B104KB8NNNC</t>
+          <t>CL10A105KB8NNNC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>C14663</t>
+          <t>C15849</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2500,7 +2489,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Decoupling debounce</t>
+          <t>Bulk</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2522,15 +2511,15 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>C13-C16</t>
+          <t>C17</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1uF</t>
+          <t>100nF</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2540,12 +2529,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>CL10A105KB8NNNC</t>
+          <t>CL10B104KB8NNNC</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>C15849</t>
+          <t>C14663</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2555,12 +2544,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Bulk</t>
+          <t>Opto RC</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>3.3V</t>
+          <t>12V</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2577,45 +2566,45 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>C17</t>
+          <t>LED1-LED12</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>100nF</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Capacitor_SMD:C_0603</t>
+          <t>LED_SMD:LED_0603</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>CL10B104KB8NNNC</t>
+          <t>19-217/R6C-AL1M2QY/3T</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>C14663</t>
+          <t>C2297</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Capacitor</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Opto RC</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>12V</t>
+          <t>3.3V</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -2632,11 +2621,11 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>LED1-LED12</t>
+          <t>LED13-LED15</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -2665,7 +2654,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2687,62 +2676,57 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>LED13-LED15</t>
+          <t>J40</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>LED</t>
+          <t>40-pin header</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LED_SMD:LED_0603</t>
+          <t>Connector_PinHeader_2.54mm:PinHeader_2x20_P2.54mm_Vertical</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>19-217/R6C-AL1M2QY/3T</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>C2297</t>
+          <t>PHA2-20</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>LED</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Raspberry Pi</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>3.3V</t>
+          <t>5V</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0603</t>
+          <t>TH</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>SMT</t>
+          <t>TH</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>J40</t>
+          <t>J41</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -2750,28 +2734,32 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>40-pin header</t>
+          <t>DNP</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Connector_PinHeader_2.54mm:PinHeader_2x20_P2.54mm_Vertical</t>
+          <t>DNP</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>PHA2-20</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr"/>
+          <t>HRO-TYPE-C-31-M-12</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>C165948</t>
+        </is>
+      </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>DNP v1 - Pi fed via J40 header 5V</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Raspberry Pi</t>
+          <t>Optional Pi power</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2781,62 +2769,52 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>SMT</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>SMT</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>J41</t>
+          <t>TP1-TP10</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>USB-C</t>
+          <t>TestPad</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Connector_USB:USB_C_Receptacle</t>
+          <t>TestPoint:TestPoint_Pad_SMD</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>HRO-TYPE-C-31-M-12</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>C165948</t>
+          <t>TP_SMD</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>TestPoint</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Optional Pi power</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>5V</t>
+          <t>Debug</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>SMT</t>
+          <t>SMD</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -2848,94 +2826,470 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>TP1-TP10</t>
+          <t>MH1-MH4</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>TestPad</t>
+          <t>MountingHole</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>TestPoint:TestPoint_Pad_SMD</t>
+          <t>MountingHole:MountingHole_3.2mm</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>TP_SMD</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr"/>
+          <t>MH3.2</t>
+        </is>
+      </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>TestPoint</t>
+          <t>Mechanical</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Debug</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>Mounting</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>SMD</t>
+          <t>NPTH</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>SMT</t>
+          <t>TH</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MH1-MH4</t>
+          <t>J17</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MountingHole</t>
+          <t>KF301-2P</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>MountingHole:MountingHole_3.2mm</t>
+          <t>TerminalBlock_Phoenix:TerminalBlock_MKDS-2-5.08_1x02_P5.08mm</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>MH3.2</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
+          <t>KF301-2P</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>C474892</t>
+        </is>
+      </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Mechanical</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Mounting</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>5V screw input</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>5V</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>NPTH</t>
+          <t>TH</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
           <t>TH</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2A</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Fuse:Fuse_1206-3216Metric</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2A</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>C72043</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Protection</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>5V input fuse</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>5V</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>1206</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>500mA</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Fuse:Fuse_1206-3216Metric</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>500mA</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>C369233</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Protection</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>HDMI pin18 polyfuse</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>5V</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>1206</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1N4001</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Diode_THT:D_DO-41_SOD81_P7.62mm_Horizontal</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>1N4001</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>C81598</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Protection</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>5V reverse block</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>5V</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>DO-41</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>PN2222A</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Package_TO_SOT_SMD:SOT-23</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>PN2222A-TA</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>C2150</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Transistor</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>SSR master safety BCM4</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>12V</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>SOT-23</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>R34</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>10k</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0603WAF1002T5E</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>EXP_B P3 pull-up</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>R35</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>10k</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>0603WAF1002T5E</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>EXP_B P4 pull-up</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>R36</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>10k</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>0603WAF1002T5E</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>EXP_B P5 pull-up</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>SMT</t>
         </is>
       </c>
     </row>

--- a/projects/wanos-board/components.xlsx
+++ b/projects/wanos-board/components.xlsx
@@ -2,15 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -46,11 +45,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -122,6 +122,30 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="components" displayName="components" ref="A1:L105" headerRowCount="1" totalsRowShown="0">
+  <autoFilter ref="A1:L105"/>
+  <sortState ref="A2:L105">
+    <sortCondition ref="A1:A105"/>
+  </sortState>
+  <tableColumns count="12">
+    <tableColumn id="1" name="Designator"/>
+    <tableColumn id="12" name="type"/>
+    <tableColumn id="2" name="Quantity"/>
+    <tableColumn id="3" name="Value"/>
+    <tableColumn id="4" name="Footprint"/>
+    <tableColumn id="5" name="MPN"/>
+    <tableColumn id="6" name="LCSC"/>
+    <tableColumn id="7" name="Category"/>
+    <tableColumn id="8" name="Comment"/>
+    <tableColumn id="9" name="Voltage"/>
+    <tableColumn id="10" name="Package"/>
+    <tableColumn id="11" name="MountType"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -413,8 +437,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K54"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:L105"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9.28515625" defaultRowHeight="15"/>
+  <cols>
+    <col width="12.85546875" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
+    <col width="12.85546875" customWidth="1" style="1" min="2" max="2"/>
+    <col width="11" bestFit="1" customWidth="1" style="1" min="3" max="3"/>
+    <col width="23.42578125" bestFit="1" customWidth="1" style="1" min="4" max="4"/>
+    <col width="63.140625" bestFit="1" customWidth="1" style="1" min="5" max="5"/>
+    <col width="23.140625" bestFit="1" customWidth="1" style="1" min="6" max="6"/>
+    <col width="9.140625" bestFit="1" customWidth="1" style="1" min="7" max="7"/>
+    <col width="30.28515625" bestFit="1" customWidth="1" style="1" min="8" max="8"/>
+    <col width="56.42578125" bestFit="1" customWidth="1" style="1" min="9" max="9"/>
+    <col width="10.140625" bestFit="1" customWidth="1" style="1" min="10" max="10"/>
+    <col width="15.7109375" bestFit="1" customWidth="1" style="1" min="11" max="11"/>
+    <col width="13.5703125" bestFit="1" customWidth="1" style="1" min="12" max="12"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -424,50 +462,55 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>Quantity</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Footprint</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>MPN</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>LCSC</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Voltage</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Package</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>MountType</t>
         </is>
@@ -476,53 +519,58 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J1</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>HDMI Molex 208658-1052</t>
-        </is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>capacitor</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Connector_HDMI:HDMI_Molex_208658-1052</t>
+          <t>100u</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>208658-1052</t>
+          <t>Capacitor_SMD:CP_Elec_6.3x5.4mm</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>C6990958</t>
+          <t>RVT1A101M0605</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>C72472</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>E-ink SPI HDMI</t>
+          <t>Capacitor</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5V</t>
+          <t>+5VA bulk electrolytic; place at D1/D2/F1 conditioning output</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>SMT</t>
+          <t>10V</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
+        <is>
+          <t>6.3x5.4</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>SMT</t>
         </is>
@@ -531,823 +579,898 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J2</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>JST XH 2-pin</t>
-        </is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>capacitor</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Connector_JST:JST_XH_B2B-XH-A_1x02_P2.50mm_Vertical</t>
+          <t>100n</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>B2B-XH-A</t>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>C158012</t>
+          <t>CL10B104KB8NNNC</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>C14663</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Door sauna</t>
+          <t>Capacitor</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3.3V</t>
+          <t>SSR driver snubber/decouple; place at Q3 (SSR phase U)</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>12V</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>SMT</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J3</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>JST XH 2-pin</t>
-        </is>
+          <t>C11</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>capacitor</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Connector_JST:JST_XH_B2B-XH-A_1x02_P2.50mm_Vertical</t>
+          <t>100n</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>B2B-XH-A</t>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>C158012</t>
+          <t>CL10B104KB8NNNC</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>C14663</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Door bathroom</t>
+          <t>Capacitor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3.3V</t>
+          <t>SSR driver snubber/decouple; place at Q4 (SSR IR)</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>12V</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>SMT</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J4</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>JST XH 6-pin</t>
-        </is>
+          <t>C12</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>capacitor</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Connector_JST:JST_XH_B6B-XH-A_1x06_P2.50mm_Vertical</t>
+          <t>100n</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>B6B-XH-A</t>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>C158014</t>
+          <t>CL10B104KB8NNNC</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>C14663</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Water meters B1</t>
+          <t>Capacitor</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3.3V</t>
+          <t>SSR driver snubber/decouple; place at Q5 (SSR safety)</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>12V</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>SMT</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J5</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>JST XH 6-pin</t>
-        </is>
+          <t>C17</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>capacitor</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Connector_JST:JST_XH_B6B-XH-A_1x06_P2.50mm_Vertical</t>
+          <t>100n</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>B6B-XH-A</t>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>C158014</t>
+          <t>CL10B104KB8NNNC</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>C14663</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Water meters B2</t>
+          <t>Capacitor</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3.3V</t>
+          <t>Opto RC filter; place at U4 with R33</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>12V</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>SMT</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J6</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>JST XH 2-pin</t>
-        </is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>capacitor</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Connector_JST:JST_XH_B2B-XH-A_1x02_P2.50mm_Vertical</t>
+          <t>100n</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>B2B-XH-A</t>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>C158012</t>
+          <t>CL10B104KB8NNNC</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>C14663</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>kWh main</t>
+          <t>Capacitor</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3.3V</t>
+          <t>+5VA HF bypass; place with C1 at +5VA node</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>5V</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>SMT</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J7</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>JST XH 2-pin</t>
-        </is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>capacitor</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Connector_JST:JST_XH_B2B-XH-A_1x02_P2.50mm_Vertical</t>
+          <t>100n</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>B2B-XH-A</t>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>C158012</t>
+          <t>CL10B104KB8NNNC</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>C14663</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>kWh aux</t>
+          <t>Capacitor</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>U1 (PCA9554) VCC decouple; place at U1 pin 16</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>3.3V</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>TH</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>SMT</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J8</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>JST XH 4-pin</t>
-        </is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>capacitor</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Connector_JST:JST_XH_B4B-XH-A_1x04_P2.50mm_Vertical</t>
+          <t>100n</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>B4B-XH-A</t>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>C158016</t>
+          <t>CL10B104KB8NNNC</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>C14663</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sauna LCD buttons Cat5</t>
+          <t>Capacitor</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>U2 (PCA9554) VCC decouple; place at U2 pin 16</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>3.3V</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>TH</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>SMT</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J9</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>JST XH 4-pin</t>
-        </is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>capacitor</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Connector_JST:JST_XH_B4B-XH-A_1x04_P2.50mm_Vertical</t>
+          <t>100n</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>B4B-XH-A</t>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>C158016</t>
+          <t>CL10B104KB8NNNC</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>C14663</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>SHT31 bathroom mux ch0</t>
+          <t>Capacitor</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>U2 VCC (verify vs C4 at layout); schematic at U2 row</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>3.3V</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>TH</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>SMT</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J10</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>JST XH 4-pin</t>
-        </is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>capacitor</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Connector_JST:JST_XH_B4B-XH-A_1x04_P2.50mm_Vertical</t>
+          <t>100n</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>B4B-XH-A</t>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>C158016</t>
+          <t>CL10B104KB8NNNC</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>C14663</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>SHT31 cinema mux ch1</t>
+          <t>Capacitor</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>U5 (TCA9546A) VCC decouple; place at U5 pin 16</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>3.3V</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>TH</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>SMT</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J11</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>JST XH 4-pin</t>
-        </is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>capacitor</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Connector_JST:JST_XH_B4B-XH-A_1x04_P2.50mm_Vertical</t>
+          <t>1u</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>B4B-XH-A</t>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>C158016</t>
+          <t>CL10A105KB8NNNC</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>C15849</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>SHT31 sauna mid mux ch2</t>
+          <t>Capacitor</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>U5 bulk; place at U5 with C6</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>3.3V</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>TH</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>SMT</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J12</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>JST XH 4-pin</t>
-        </is>
+          <t>C8</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>capacitor</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Connector_JST:JST_XH_B4B-XH-A_1x04_P2.50mm_Vertical</t>
+          <t>100n</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>B4B-XH-A</t>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>C158016</t>
+          <t>CL10B104KB8NNNC</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>C14663</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>SHT31 sauna high mux ch3</t>
+          <t>Capacitor</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.3V</t>
+          <t>SSR driver snubber/decouple; place at Q1 (SSR phase W)</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>12V</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>SMT</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J13</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>JST XH 5-pin</t>
-        </is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>capacitor</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Connector_JST:JST_XH_B5B-XH-A_1x05_P2.50mm_Vertical</t>
+          <t>100n</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>B5B-XH-A</t>
+          <t>Capacitor_SMD:C_0805_2012Metric</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>C158018</t>
+          <t>CL10B104KB8NNNC</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>C14663</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>SSR field WISC parity</t>
+          <t>Capacitor</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
+          <t>SSR driver snubber/decouple; place at Q2 (SSR phase V)</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>12V</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>TH</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>SMT</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J14</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>KF301-2P</t>
-        </is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>diode</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>TerminalBlock_Phoenix_MKDS-2-5.08_1x02_P5.08mm</t>
+          <t>BZT52C5V6</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>KF301-2P</t>
+          <t>Diode_SMD:D_SOD-123</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>C39545</t>
+          <t>BZT52C5V6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>C173406</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>12V input</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>12V</t>
+          <t>5 V zener conditioning (SMD; 500mW)</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>5.6V</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>SOD-123</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>SMT</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J16</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>JST XH 4-pin</t>
-        </is>
+          <t>D11</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>diode</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Connector_JST:JST_XH_B4B-XH-A_1x04_P2.50mm_Vertical</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>B4B-XH-A</t>
+          <t>LED_SMD:LED_0603</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>C158016</t>
+          <t>19-217/R6C-AL1M2QY/3T</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>C2297</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>LCD I2C both paralleled</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
+          <t>Activity door sauna J2; with R17; place at U1/field-input zone</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>3.3V</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>TH</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>SMT</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>U1</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>PCA9554PW</t>
-        </is>
+          <t>D12</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>diode</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Package_SO:TSSOP-16_4.4x5mm_P0.65mm</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PCA9554PW</t>
+          <t>LED_SMD:LED_0603</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>C112612</t>
+          <t>19-217/R6C-AL1M2QY/3T</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>C2297</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>I/O Expander A</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
+          <t>Activity door bathroom J3; with R18</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
           <t>3.3V</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>TSSOP-16</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>SMT</t>
         </is>
@@ -1356,53 +1479,58 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>U2</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>PCA9554PW</t>
-        </is>
+          <t>D13</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>diode</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Package_SO:TSSOP-16_4.4x5mm_P0.65mm</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PCA9554PW</t>
+          <t>LED_SMD:LED_0603</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>C112612</t>
+          <t>19-217/R6C-AL1M2QY/3T</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>C2297</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>I/O Expander B</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
+          <t>Activity water B1 cold J4; with R19</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
           <t>3.3V</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>TSSOP-16</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>SMT</t>
         </is>
@@ -1411,53 +1539,58 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>U4</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>PC817 SMD</t>
-        </is>
+          <t>D14</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>diode</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Optocoupler_SO-4</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>PC817X</t>
+          <t>LED_SMD:LED_0603</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>C106900</t>
+          <t>19-217/R6C-AL1M2QY/3T</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Optocoupler</t>
+          <t>C2297</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>12V presence</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>12V</t>
+          <t>Activity water B1 hot J4; with R20</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>SO-4</t>
+          <t>3.3V</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t>SMT</t>
         </is>
@@ -1466,53 +1599,58 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>U5</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>TCA9546A</t>
-        </is>
+          <t>D15</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>diode</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Package_SO:TSSOP-16_4.4x5mm_P0.65mm</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>TCA9546APWR</t>
+          <t>LED_SMD:LED_0603</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>C133008</t>
+          <t>19-217/R6C-AL1M2QY/3T</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>IC</t>
+          <t>C2297</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>I2C mux 4ch SHT31</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
+          <t>Activity water B2 cold J5; with R21</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
           <t>3.3V</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>TSSOP-16</t>
-        </is>
-      </c>
       <c r="K20" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t>SMT</t>
         </is>
@@ -1521,53 +1659,58 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Q1</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>PN2222A</t>
-        </is>
+          <t>D16</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>diode</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Package_TO_SOT_SMD:SOT-23</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>PN2222A-TA</t>
+          <t>LED_SMD:LED_0603</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>C2150</t>
+          <t>19-217/R6C-AL1M2QY/3T</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Transistor</t>
+          <t>C2297</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>SSR driver</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>12V</t>
+          <t>Activity water B2 hot J5; with R22</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>SOT-23</t>
+          <t>3.3V</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>SMT</t>
         </is>
@@ -1576,53 +1719,58 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Q2</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>PN2222A</t>
-        </is>
+          <t>D17</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>diode</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Package_TO_SOT_SMD:SOT-23</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>PN2222A-TA</t>
+          <t>LED_SMD:LED_0603</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>C2150</t>
+          <t>19-217/R6C-AL1M2QY/3T</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Transistor</t>
+          <t>C2297</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>SSR driver</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>12V</t>
+          <t>Activity kWh main J6; with R23</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>SOT-23</t>
+          <t>3.3V</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t>SMT</t>
         </is>
@@ -1631,53 +1779,58 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Q3</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>1</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>PN2222A</t>
-        </is>
+          <t>D18</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>diode</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Package_TO_SOT_SMD:SOT-23</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>PN2222A-TA</t>
+          <t>LED_SMD:LED_0603</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>C2150</t>
+          <t>19-217/R6C-AL1M2QY/3T</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Transistor</t>
+          <t>C2297</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>SSR driver</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>12V</t>
+          <t>Activity kWh aux J7; with R24</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>SOT-23</t>
+          <t>3.3V</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
         <is>
           <t>SMT</t>
         </is>
@@ -1686,53 +1839,58 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Q4</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>1</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>PN2222A</t>
-        </is>
+          <t>D19</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>diode</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Package_TO_SOT_SMD:SOT-23</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>PN2222A-TA</t>
+          <t>LED_SMD:LED_0603</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>C2150</t>
+          <t>19-217/R6C-AL1M2QY/3T</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Transistor</t>
+          <t>C2297</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>SSR driver</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>12V</t>
+          <t>Activity SSR phase W / Q1; with R25; bottom SSR zone</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>SOT-23</t>
+          <t>3.3V</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
         <is>
           <t>SMT</t>
         </is>
@@ -1741,53 +1899,58 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>D1</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>1</v>
-      </c>
-      <c r="C25" t="inlineStr">
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>diode</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>SMBJ12A</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Diode_SMD:D_SMB</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>SMBJ12A</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>C149934</t>
-        </is>
-      </c>
       <c r="G25" t="inlineStr">
         <is>
+          <t>C353398</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
           <t>Protection</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>12V TVS</t>
-        </is>
-      </c>
       <c r="I25" t="inlineStr">
         <is>
+          <t>12 V TVS (+12VA / GND at 12 V entry)</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
           <t>12V</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>SMB</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>SMT</t>
         </is>
@@ -1796,53 +1959,58 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>FB1</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>BLM21PG331SN1</t>
-        </is>
+          <t>D20</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>diode</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Inductor_SMD:L_0805</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>BLM21PG331SN1</t>
+          <t>LED_SMD:LED_0603</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>C85832</t>
+          <t>19-217/R6C-AL1M2QY/3T</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Ferrite</t>
+          <t>C2297</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Pi 5V filter</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>5V</t>
+          <t>Activity SSR phase V / Q2; with R26</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0805</t>
+          <t>3.3V</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
         <is>
           <t>SMT</t>
         </is>
@@ -1851,48 +2019,58 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>470R</t>
-        </is>
+          <t>D21</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>diode</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Resistor_SMD:R_0603</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0603WAF4700T5E</t>
+          <t>LED_SMD:LED_0603</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>19-217/R6C-AL1M2QY/3T</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Resistor</t>
+          <t>C2297</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>SSR base</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
+          <t>Activity SSR phase U / Q3; with R27</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
           <t>3.3V</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>0603</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>SMT</t>
         </is>
@@ -1901,48 +2079,58 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>1</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>470R</t>
-        </is>
+          <t>D22</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>diode</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Resistor_SMD:R_0603</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0603WAF4700T5E</t>
+          <t>LED_SMD:LED_0603</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>19-217/R6C-AL1M2QY/3T</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Resistor</t>
+          <t>C2297</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>SSR base</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
+          <t>Activity SSR IR / Q4; with R28</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
           <t>3.3V</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>0603</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>SMT</t>
         </is>
@@ -1951,48 +2139,58 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>R3</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>1</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>470R</t>
-        </is>
+          <t>D23</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>diode</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Resistor_SMD:R_0603</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0603WAF4700T5E</t>
+          <t>LED_SMD:LED_0603</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>19-217/R6C-AL1M2QY/3T</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Resistor</t>
+          <t>C2297</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>SSR base</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3.3V</t>
+          <t>Status 5V in (+5VA post-F1); with R29 2k0; Pi power zone</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
+          <t>5V</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t>0603</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>SMT</t>
         </is>
@@ -2001,48 +2199,58 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>R4</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>470R</t>
-        </is>
+          <t>D24</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>diode</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Resistor_SMD:R_0603</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0603WAF4700T5E</t>
+          <t>LED_SMD:LED_0603</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>19-217/R6C-AL1M2QY/3T</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Resistor</t>
+          <t>C2297</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>SSR base</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>3.3V</t>
+          <t>Status 12V (+12VA J14); with R30 6k8; bottom power zone</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
+          <t>12V</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t>0603</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>SMT</t>
         </is>
@@ -2051,48 +2259,58 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>R5-R8</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>4</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>10k</t>
-        </is>
+          <t>D25</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>diode</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Resistor_SMD:R_0603</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0603WAF1002T5E</t>
+          <t>LED_SMD:LED_0603</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>19-217/R6C-AL1M2QY/3T</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Resistor</t>
+          <t>C2297</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>SSR pulldown</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3.3V</t>
+          <t>Status 5V Pi (+5VA J40); with R31 2k0; near J40</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
+          <t>5V</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t>0603</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>SMT</t>
         </is>
@@ -2101,48 +2319,58 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>R9</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>1</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>2k2</t>
-        </is>
+          <t>F1</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>polyfuse</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Resistor_SMD:R_0603</t>
+          <t>2A</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0603WAF2201T5E</t>
+          <t>Fuse:Fuse_1206_3216Metric</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>SMD1206P200TF</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Resistor</t>
+          <t>C545216</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>I2C SCL pull-up</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3.3V</t>
+          <t>5V input polyfuse 2A hold</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0603</t>
+          <t>5V</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
+        <is>
+          <t>1206</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
         <is>
           <t>SMT</t>
         </is>
@@ -2151,48 +2379,58 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>R10</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>2k2</t>
-        </is>
+          <t>F2</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>fuse</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Resistor_SMD:R_0603</t>
+          <t>500mA</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0603WAF2201T5E</t>
+          <t>Fuse:Fuse_1206-3216Metric</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>500mA</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Resistor</t>
+          <t>C369233</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>I2C SDA pull-up</t>
+          <t>Protection</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>3.3V</t>
+          <t>HDMI pin18 polyfuse</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0603</t>
+          <t>5V</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
+        <is>
+          <t>1206</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
         <is>
           <t>SMT</t>
         </is>
@@ -2201,48 +2439,58 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>R17-R28</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>12</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>1k0</t>
-        </is>
+          <t>FB1</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ferrite</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Resistor_SMD:R_0603</t>
+          <t>BLM21PG331SN1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0603WAF3300T5E</t>
+          <t>Inductor_SMD:L_0805</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>BLM21PG331SN1</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Resistor</t>
+          <t>C85832</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Activity LED</t>
+          <t>Ferrite</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>3.3V</t>
+          <t>Pi 5V filter</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0603</t>
+          <t>5V</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
+        <is>
+          <t>0805</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
         <is>
           <t>SMT</t>
         </is>
@@ -2251,48 +2499,58 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>R29-R31</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>3</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>R29/R31=2k0 R30=6k8</t>
-        </is>
+          <t>J1</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Resistor_SMD:R_0603</t>
+          <t>HDMI Molex 208658-1052</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0603WAF2201T5E</t>
+          <t>Connector_HDMI:HDMI_Molex_208658-1052</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>208658-1052</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Resistor</t>
+          <t>C6990958</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Status LED</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3.3V</t>
+          <t>E-ink SPI HDMI</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0603</t>
+          <t>5V</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
         <is>
           <t>SMT</t>
         </is>
@@ -2301,423 +2559,478 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>R32</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>1k5</t>
-        </is>
+          <t>J10</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Resistor_SMD:R_0603</t>
+          <t>JST XH 4-pin</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0603WAF2001T5E</t>
+          <t>Connector_JST:JST_XH_B4B-XH-A_1x04_P2.50mm_Vertical</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>B4B-XH-A</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Resistor</t>
+          <t>C158016</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Opto LED</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>12V</t>
+          <t>SHT31 cinema mux ch1</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0603</t>
+          <t>3.3V</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>SMT</t>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>TH</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>R33</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>10k</t>
-        </is>
+          <t>J11</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Resistor_SMD:R_0603</t>
+          <t>JST XH 4-pin</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0603WAF1002T5E</t>
+          <t>Connector_JST:JST_XH_B4B-XH-A_1x04_P2.50mm_Vertical</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>B4B-XH-A</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Resistor</t>
+          <t>C158016</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Opto RC filter</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>12V</t>
+          <t>SHT31 sauna mid mux ch2</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0603</t>
+          <t>3.3V</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>SMT</t>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>TH</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>C1-C12</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>12</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>100nF</t>
-        </is>
+          <t>J12</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Capacitor_SMD:C_0603</t>
+          <t>JST XH 4-pin</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>CL10B104KB8NNNC</t>
+          <t>Connector_JST:JST_XH_B4B-XH-A_1x04_P2.50mm_Vertical</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>C14663</t>
+          <t>B4B-XH-A</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Capacitor</t>
+          <t>C158016</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Decoupling debounce</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
+          <t>SHT31 sauna high mux ch3</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
           <t>3.3V</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>0603</t>
-        </is>
-      </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>SMT</t>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>TH</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>C13-C16</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>4</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>1uF</t>
-        </is>
+          <t>J13</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Capacitor_SMD:C_0603</t>
+          <t>JST XH 5-pin</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>CL10A105KB8NNNC</t>
+          <t>Connector_JST:JST_XH_B5B-XH-A_1x05_P2.50mm_Vertical</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>C15849</t>
+          <t>B5B-XH-A</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Capacitor</t>
+          <t>C158018</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Bulk</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>3.3V</t>
+          <t>SSR field WISC parity</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0603</t>
+          <t>12V</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>SMT</t>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>TH</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>C17</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>100nF</t>
-        </is>
+          <t>J14</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Capacitor_SMD:C_0603</t>
+          <t>KF301-2P</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>CL10B104KB8NNNC</t>
+          <t>TerminalBlock_Phoenix_MKDS-2-5.08_1x02_P5.08mm</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>C14663</t>
+          <t>KF301-2P</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Capacitor</t>
+          <t>C39545</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Opto RC</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
+          <t>12V input</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
           <t>12V</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>0603</t>
-        </is>
-      </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>SMT</t>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>TH</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>LED1-LED12</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>12</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>LED</t>
-        </is>
+          <t>J16</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LED_SMD:LED_0603</t>
+          <t>JST XH 4-pin</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>19-217/R6C-AL1M2QY/3T</t>
+          <t>Connector_JST:JST_XH_B4B-XH-A_1x04_P2.50mm_Vertical</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>C2297</t>
+          <t>B4B-XH-A</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>LED</t>
+          <t>C158016</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
+          <t>LCD I2C both paralleled</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
           <t>3.3V</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>0603</t>
-        </is>
-      </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>SMT</t>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>TH</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>LED13-LED15</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>3</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>LED</t>
-        </is>
+          <t>J17</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LED_SMD:LED_0603</t>
+          <t>KF301-2P</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>19-217/R6C-AL1M2QY/3T</t>
+          <t>TerminalBlock_Phoenix:TerminalBlock_MKDS-2-5.08_1x02_P5.08mm</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>C2297</t>
+          <t>KF301-2P</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>LED</t>
+          <t>C474892</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>3.3V</t>
+          <t>5V screw input</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0603</t>
+          <t>5V</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>SMT</t>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>TH</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>J40</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>1</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>40-pin header</t>
-        </is>
+          <t>J2</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>1</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Connector_PinHeader_2.54mm:PinHeader_2x20_P2.54mm_Vertical</t>
+          <t>JST XH 2-pin</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>PHA2-20</t>
+          <t>Connector_JST:JST_XH_B2B-XH-A_1x02_P2.50mm_Vertical</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>B2B-XH-A</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
+          <t>C158012</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
           <t>Connector</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Raspberry Pi</t>
-        </is>
-      </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>5V</t>
+          <t>Door sauna</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t>TH</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>TH</t>
         </is>
@@ -2726,143 +3039,173 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>J41</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>1</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>DNP</t>
-        </is>
+          <t>J3</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>DNP</t>
+          <t>JST XH 2-pin</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>HRO-TYPE-C-31-M-12</t>
+          <t>Connector_JST:JST_XH_B2B-XH-A_1x02_P2.50mm_Vertical</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>C165948</t>
+          <t>B2B-XH-A</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>DNP v1 - Pi fed via J40 header 5V</t>
+          <t>C158012</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Optional Pi power</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>5V</t>
+          <t>Door bathroom</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>SMT</t>
+          <t>3.3V</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>SMT</t>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>TH</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>TP1-TP10</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>10</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>TestPad</t>
-        </is>
+          <t>J4</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>1</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>TestPoint:TestPoint_Pad_SMD</t>
+          <t>JST XH 6-pin</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>TP_SMD</t>
+          <t>Connector_JST:JST_XH_B6B-XH-A_1x06_P2.50mm_Vertical</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>B6B-XH-A</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>TestPoint</t>
+          <t>C158014</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Debug</t>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Water meters B1</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>SMD</t>
+          <t>3.3V</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>SMT</t>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>TH</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MH1-MH4</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>4</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>MountingHole</t>
-        </is>
+          <t>J40</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>1</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>MountingHole:MountingHole_3.2mm</t>
+          <t>40-pin header</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>MH3.2</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Mechanical</t>
+          <t>Connector_PinHeader_2.54mm:PinHeader_2x20_P2.54mm_Vertical</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>PHA2-20</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Mounting</t>
+          <t>Connector</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Raspberry Pi</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>NPTH</t>
+          <t>5V</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
         <is>
           <t>TH</t>
         </is>
@@ -2871,218 +3214,238 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>J17</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>KF301-2P</t>
-        </is>
+          <t>J41</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>TerminalBlock_Phoenix:TerminalBlock_MKDS-2-5.08_1x02_P5.08mm</t>
+          <t>DNP</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>KF301-2P</t>
+          <t>DNP</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>C474892</t>
+          <t>HRO-TYPE-C-31-M-12</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Connector</t>
+          <t>C165948</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>5V screw input</t>
+          <t>DNP v1 - Pi fed via J40 header 5V</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
+          <t>Optional Pi power</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
           <t>5V</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>TH</t>
-        </is>
-      </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>SMT</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>SMT</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>F1</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>1</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>2A</t>
-        </is>
+          <t>J5</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>1</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Fuse:Fuse_1206-3216Metric</t>
+          <t>JST XH 6-pin</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2A</t>
+          <t>Connector_JST:JST_XH_B6B-XH-A_1x06_P2.50mm_Vertical</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>C72043</t>
+          <t>B6B-XH-A</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>C158014</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>5V input fuse</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>5V</t>
+          <t>Water meters B2</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>1206</t>
+          <t>3.3V</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>SMT</t>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>TH</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>F2</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>1</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>500mA</t>
-        </is>
+          <t>J6</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Fuse:Fuse_1206-3216Metric</t>
+          <t>JST XH 2-pin</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>500mA</t>
+          <t>Connector_JST:JST_XH_B2B-XH-A_1x02_P2.50mm_Vertical</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>C369233</t>
+          <t>B2B-XH-A</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>C158012</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>HDMI pin18 polyfuse</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>5V</t>
+          <t>kWh main</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>1206</t>
+          <t>3.3V</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>SMT</t>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>TH</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>D2</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>1</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>1N4001</t>
-        </is>
+          <t>J7</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Diode_THT:D_DO-41_SOD81_P7.62mm_Horizontal</t>
+          <t>JST XH 2-pin</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1N4001</t>
+          <t>Connector_JST:JST_XH_B2B-XH-A_1x02_P2.50mm_Vertical</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>C81598</t>
+          <t>B2B-XH-A</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Protection</t>
+          <t>C158012</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>5V reverse block</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>5V</t>
+          <t>kWh aux</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>DO-41</t>
+          <t>3.3V</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
         <is>
           <t>TH</t>
         </is>
@@ -3091,203 +3454,3073 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Q5</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>1</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>PN2222A</t>
-        </is>
+          <t>J8</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Package_TO_SOT_SMD:SOT-23</t>
+          <t>JST XH 4-pin</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>PN2222A-TA</t>
+          <t>Connector_JST:JST_XH_B4B-XH-A_1x04_P2.50mm_Vertical</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>C2150</t>
+          <t>B4B-XH-A</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Transistor</t>
+          <t>C158016</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>SSR master safety BCM4</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>12V</t>
+          <t>Sauna LCD buttons Cat5</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>SOT-23</t>
+          <t>3.3V</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>SMT</t>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>TH</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>R34</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>1</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>10k</t>
-        </is>
+          <t>J9</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Resistor_SMD:R_0603</t>
+          <t>JST XH 4-pin</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0603WAF1002T5E</t>
+          <t>Connector_JST:JST_XH_B4B-XH-A_1x04_P2.50mm_Vertical</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>B4B-XH-A</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Resistor</t>
+          <t>C158016</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>EXP_B P3 pull-up</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
+          <t>SHT31 bathroom mux ch0</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
           <t>3.3V</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>0603</t>
-        </is>
-      </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>SMT</t>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>TH</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>R35</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>1</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>10k</t>
-        </is>
+          <t>MH1-MH4</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>mountinghole</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>4</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Resistor_SMD:R_0603</t>
+          <t>MountingHole</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0603WAF1002T5E</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Resistor</t>
+          <t>MountingHole:MountingHole_3.2mm</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>MH3.2</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>EXP_B P4 pull-up</t>
+          <t>Mechanical</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>3.3V</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>0603</t>
+          <t>Mounting</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>SMT</t>
+          <t>NPTH</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>TH</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>transistor</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>1</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>PN2222A</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Package_TO_SOT_SMD:SOT-23</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>PN2222A-TA</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>C2150</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Transistor</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>SSR driver</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>12V</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>SOT-23</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>transistor</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>PN2222A</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Package_TO_SOT_SMD:SOT-23</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>PN2222A-TA</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>C2150</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Transistor</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>SSR driver</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>12V</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>SOT-23</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>transistor</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>PN2222A</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Package_TO_SOT_SMD:SOT-23</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>PN2222A-TA</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>C2150</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Transistor</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>SSR driver</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>12V</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>SOT-23</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>transistor</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>PN2222A</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Package_TO_SOT_SMD:SOT-23</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>PN2222A-TA</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>C2150</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Transistor</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>SSR driver</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>12V</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>SOT-23</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>transistor</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>PN2222A-TA</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Package_TO_SOT_SMD:SOT-23</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>PN2222A-TA</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>C181091</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Transistor</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>SSR master safety BCM4</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>12V</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>SOT-23</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>1</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>470R</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>0603WAF4700T5E</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Q1 SSR base; place at Q1</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>R10</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2k2</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>0603WAF2201T5E</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>I2C SDA pull-up</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>R14</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>470R</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>0603WAF4700T5E</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Q5 SSR safety base; place at Q5</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>R15</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>10k</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>0603WAF1002T5E</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>Q5 SSR safety pulldown; place at Q5</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>R17</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>1k0</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>0603WAF1001T5E</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>D11 activity LED; place at D11</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>R18</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>1k0</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>0603WAF1001T5E</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>D12 activity LED; place at D12</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>R19</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>1k0</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>0603WAF1001T5E</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>D13 activity LED; place at D13</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>470R</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>0603WAF4700T5E</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Q2 SSR base; place at Q2</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>R20</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>1k0</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>0603WAF1001T5E</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>D14 activity LED; place at D14</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>R21</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>1k0</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>0603WAF1001T5E</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>D15 activity LED; place at D15</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>R22</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>1k0</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>0603WAF1001T5E</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>D16 activity LED; place at D16</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>R23</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>1k0</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>0603WAF1001T5E</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>D17 activity LED; place at D17</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>R24</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>1k0</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>0603WAF1001T5E</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>D18 activity LED; place at D18</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>R25</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>1</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>1k0</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>0603WAF1001T5E</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>D19 activity LED; place at D19</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>R26</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>1k0</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>0603WAF1001T5E</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>D20 activity LED; place at D20</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>R27</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>1</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>1k0</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>0603WAF1001T5E</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>D21 activity LED; place at D21</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>R28</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>1k0</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>0603WAF1001T5E</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>D22 activity LED; place at D22</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>R29</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2k0</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>0603WAF2001T5E</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>D23 status 5V in; place at D23</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>5V</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>R3</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>470R</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>0603WAF4700T5E</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Q3 SSR base; place at Q3</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>R30</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>1</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>6k8</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>0603WAF6801T5E</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>D24 status 12V; place at D24</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>12V</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>R31</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>1</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2k0</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>0603WAF2001T5E</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>D25 status 5V Pi; place at D25</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>5V</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>R32</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>1</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>1k5</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>0603WAF2001T5E</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Opto LED</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>12V</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>R33</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>1</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>10k</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>0603WAF1002T5E</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Opto RC filter</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>12V</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>R34</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>1</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>10k</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>0603WAF1002T5E</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>EXP_B P3 pull-up</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>R35</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>1</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>10k</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>0603WAF1002T5E</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>EXP_B P4 pull-up</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
           <t>R36</t>
         </is>
       </c>
-      <c r="B54" t="n">
-        <v>1</v>
-      </c>
-      <c r="C54" t="inlineStr">
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>1</v>
+      </c>
+      <c r="D84" t="inlineStr">
         <is>
           <t>10k</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="E84" t="inlineStr">
         <is>
           <t>Resistor_SMD:R_0603</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="F84" t="inlineStr">
         <is>
           <t>0603WAF1002T5E</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="H84" t="inlineStr">
         <is>
           <t>Resistor</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t>EXP_B P5 pull-up</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="J84" t="inlineStr">
         <is>
           <t>3.3V</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="K84" t="inlineStr">
         <is>
           <t>0603</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>R4</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>470R</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>0603WAF4700T5E</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Q4 SSR base; place at Q4</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>R5</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>1</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>10k</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>0603WAF1002T5E</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Q1 SSR pulldown; place at Q1</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>R6</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>1</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>10k</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>0603WAF1002T5E</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Q2 SSR pulldown; place at Q2</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>R7</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>1</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>10k</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>0603WAF1002T5E</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Q3 SSR pulldown; place at Q3</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>R8</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>1</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>10k</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>0603WAF1002T5E</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Q4 SSR pulldown; place at Q4</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>R9</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>resistor</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>1</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2k2</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Resistor_SMD:R_0603</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>0603WAF2201T5E</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Resistor</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>I2C SCL pull-up</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>0603</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>TP1</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>testpoint</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>1</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>TestPad</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>TestPoint:TestPoint_Pad_SMD</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>TP_SMD</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>TestPoint</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Debug +3V3; layout L1 (not on schematic yet)</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>TP10</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>testpoint</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>1</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>TestPad</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>TestPoint:TestPoint_Pad_SMD</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>TP_SMD</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>TestPoint</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Debug spare; layout L1</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>TP2</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>testpoint</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>1</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>TestPad</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>TestPoint:TestPoint_Pad_SMD</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>TP_SMD</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>TestPoint</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Debug GND; layout L1</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>TP3</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>testpoint</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>1</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>TestPad</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>TestPoint:TestPoint_Pad_SMD</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>TP_SMD</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>TestPoint</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Debug +5VA; layout L1</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>5V</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>TP4</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>testpoint</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>1</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>TestPad</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>TestPoint:TestPoint_Pad_SMD</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>TP_SMD</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>TestPoint</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Debug +12VA; layout L1</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>12V</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>TP5</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>testpoint</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>1</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>TestPad</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>TestPoint:TestPoint_Pad_SMD</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>TP_SMD</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>TestPoint</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Debug I2C_SCL; layout L1</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>TP6</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>testpoint</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>1</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>TestPad</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>TestPoint:TestPoint_Pad_SMD</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>TP_SMD</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>TestPoint</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Debug I2C_SDA; layout L1</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>TP7</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>testpoint</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>1</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>TestPad</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>TestPoint:TestPoint_Pad_SMD</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>TP_SMD</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>TestPoint</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Debug spare; layout L1</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>TP8</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>testpoint</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>1</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>TestPad</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>TestPoint:TestPoint_Pad_SMD</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>TP_SMD</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>TestPoint</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Debug spare; layout L1</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>TP9</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>testpoint</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>1</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>TestPad</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>TestPoint:TestPoint_Pad_SMD</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>TP_SMD</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>TestPoint</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Debug spare; layout L1</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>SMD</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>U1</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>IC</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>1</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>PCA9554PW</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Package_SO:TSSOP-16_4.4x5mm_P0.65mm</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>PCA9554PW</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>C112612</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>IC</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>I/O Expander A</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>TSSOP-16</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>U2</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>IC</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>1</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>PCA9554PW</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Package_SO:TSSOP-16_4.4x5mm_P0.65mm</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>PCA9554PW</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>C112612</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>IC</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>I/O Expander B</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>TSSOP-16</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>U4</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>IC</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>1</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>PC817 SMD</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Optocoupler_SO-4</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>PC817X</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>C106900</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Optocoupler</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>12V presence</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>12V</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>SO-4</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>U5</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>IC</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>1</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>TCA9546A</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Package_SO:TSSOP-16_4.4x5mm_P0.65mm</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>TCA9546APWR</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>C133008</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>IC</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>I2C mux 4ch SHT31</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>3.3V</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>TSSOP-16</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>SMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>transistor</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>1</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>AO3401A</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Package_TO_SOT_SMD:SOT-23</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>AO3401A</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>C15127</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Transistor</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>5V ideal diode (P-FET)</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>5V</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>SOT-23</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
         <is>
           <t>SMT</t>
         </is>
@@ -3295,5 +6528,8 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>